--- a/public/outils/matrices/rent-roll-et-wault.xlsx
+++ b/public/outils/matrices/rent-roll-et-wault.xlsx
@@ -38,7 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="504">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -56,7 +56,7 @@
     <t>Un rent roll, c'est l'état locatif d'un immeuble : une ligne par lot, avec son locataire, sa surface, son loyer et ses dates. À partir de là, le classeur calcule le WAULT et le WALB, les deux durées résiduelles que publient les foncières, le taux d'occupation physique et le taux d'occupation financier, la réversion, et l'échéancier des sorties année par année.</t>
   </si>
   <si>
-    <t>Un seul onglet à remplir : Rent roll. Vous saisissez les cellules bleues, tout le reste se calcule. La Synthèse et l'Échéancier ne se saisissent pas, ils se lisent.</t>
+    <t>Un seul onglet à remplir : Rent roll. Vous saisissez les cellules violettes, tout le reste se calcule. La Synthèse et l'Échéancier ne se saisissent pas, ils se lisent.</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -176,7 +176,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu ciel, texte bleu nuit</t>
+    <t>Fond violet clair, texte violet sombre</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -194,7 +194,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond presque blanc, texte bleu nuit en gras</t>
+    <t>Fond presque blanc, texte violet sombre en gras</t>
   </si>
   <si>
     <t>Résultat de bloc, chiffre clé</t>
@@ -203,7 +203,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section, en-tête de tableau</t>
@@ -230,7 +230,7 @@
     <t>Rouge : lisez la colonne W de la ligne concernée, ou la Synthèse, qui nomme la première ligne en cause.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules bleues restent modifiables et effaçables sans rien déverrouiller. N'ôtez la protection que pour toucher une cellule blanche, par l'onglet Révision, « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules violettes restent modifiables et effaçables sans rien déverrouiller. N'ôtez la protection que pour toucher une cellule blanche, par l'onglet Révision, « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -251,7 +251,7 @@
     <t>Rent roll!B11:G50, Rent roll!I11:I50, Rent roll!M11:P50, Rent roll!R11:R50, Rent roll!C7</t>
   </si>
   <si>
-    <t>Le classeur est livré rempli d'un exemple : un immeuble de 1 755 m² avec sept lots. Gardez-le pour vous repérer, ou effacez les sept lignes de l'exemple avant de saisir votre immeuble. Les colonnes bleues d'une ligne ne sont pas contiguës : sélectionnez Rent roll!B11:G17, Rent roll!I11:I17, Rent roll!M11:P17 et Rent roll!R11:R17, en maintenant la touche Ctrl pour ajouter chaque bloc à la sélection, puis appuyez sur Suppr. Les colonnes H, J, K, L et Q sont des formules verrouillées : si vous les incluez dans la sélection, Excel refuse l'effacement entier et affiche un message de protection. Elles se videront d'elles-mêmes. Videz toujours une ligne de bail en entier : une ligne à demi effacée reste comptée comme renseignée, passe au rouge et bloque le contrôle d'ensemble. La grille accepte 40 baux, lignes 11 à 50 : pour ajouter un lot, servez-vous de la première ligne bleue libre, elles sont déjà prêtes et il n'y a aucune ligne à insérer. Vérifiez surtout les saisies facultatives, qui n'ont pas de raison d'être dans votre cas : la périodicité de sortie (Rent roll!O11:O50, à ne remplir que pour un bail ayant renoncé à ses triennales), la sortie forcée (Rent roll!P11:P50) et la franchise (Rent roll!R11:R50). Pendant que vous effacez, les contrôles passent au rouge et les totaux tombent : c'est normal, tout revient dès que la saisie est complète.</t>
+    <t>Le classeur est livré rempli d'un exemple : un immeuble de 1 755 m² avec sept lots. Gardez-le pour vous repérer, ou effacez les sept lignes de l'exemple avant de saisir votre immeuble. Les colonnes violettes d'une ligne ne sont pas contiguës : sélectionnez Rent roll!B11:G17, Rent roll!I11:I17, Rent roll!M11:P17 et Rent roll!R11:R17, en maintenant la touche Ctrl pour ajouter chaque bloc à la sélection, puis appuyez sur Suppr. Les colonnes H, J, K, L et Q sont des formules verrouillées : si vous les incluez dans la sélection, Excel refuse l'effacement entier et affiche un message de protection. Elles se videront d'elles-mêmes. Videz toujours une ligne de bail en entier : une ligne à demi effacée reste comptée comme renseignée, passe au rouge et bloque le contrôle d'ensemble. La grille accepte 40 baux, lignes 11 à 50 : pour ajouter un lot, servez-vous de la première ligne violette libre, elles sont déjà prêtes et il n'y a aucune ligne à insérer. Vérifiez surtout les saisies facultatives, qui n'ont pas de raison d'être dans votre cas : la périodicité de sortie (Rent roll!O11:O50, à ne remplir que pour un bail ayant renoncé à ses triennales), la sortie forcée (Rent roll!P11:P50) et la franchise (Rent roll!R11:R50). Pendant que vous effacez, les contrôles passent au rouge et les totaux tombent : c'est normal, tout revient dès que la saisie est complète.</t>
   </si>
   <si>
     <t>Une saisie résiduelle de l'exemple est l'erreur la plus probable d'un premier usage, et les deux colonnes facultatives ne se trahissent pas de la même façon. Une périodicité de six ans héritée allonge le WALB et gonfle le loyer économique, parce que la franchise s'étale alors sur 72 mois au lieu de 36. Une franchise héritée, elle, ne touche pas au WALB, qui ne dépend que des dates : elle rabote le loyer économique. Trois mois hérités sur un lot à 119 700 € lui retirent 9 975 € par an. Dans les deux cas, aucun contrôle ne s'allume.</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les benchmarks (périodicité légale, préavis, indices Insee, seuils d'alerte, repères de durée résiduelle, garde-fous de saisie) changent avec la réglementation ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (date d'analyse, lots, locataires, surfaces, loyers, valeurs locatives, dates, franchises) sont propres à chaque immeuble. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les benchmarks (périodicité légale, préavis, indices Insee, seuils d'alerte, repères de durée résiduelle, garde-fous de saisie) changent avec la réglementation ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (date d'analyse, lots, locataires, surfaces, loyers, valeurs locatives, dates, franchises) sont propres à chaque immeuble. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
     <t>Les chiffres cités dans ce guide et dans Méthode sont écrits en toutes lettres et datés du millésime 2026 : relisez-les à chaque mise à jour de Paramètres, en particulier les repères de durée résiduelle des foncières et les seuils de la colonne « Repère métier » ci-dessus. Les libellés de source de Paramètres et de Méthode, eux, se reconstruisent seuls à partir des trois cellules de millésime (Paramètres!C38:C40).</t>
@@ -674,7 +674,7 @@
     <t>Vous préparez un plan d'asset management</t>
   </si>
   <si>
-    <t>Pour voir dans l'ordre les baux à renégocier, triez la grille sur la colonne Q. Le tri demande d'ôter d'abord la protection de la feuille, par l'onglet Révision, sans mot de passe : Excel refuse de trier une plage qui contient des colonnes calculées, et ce sont justement elles qui doivent suivre leur ligne. Sélectionnez toujours la plage entière, Rent roll!B11:X50, colonnes calculées comprises : si vous ne triez que les colonnes bleues, les colonnes blanches restent en place et chaque ligne se retrouve avec les calculs d'une autre. Remettez la protection ensuite. Pour filtrer, rien à ôter : le filtre automatique est en place sur la ligne d'en-tête et la protection l'autorise. Pour chaque bail, la colonne L dit s'il faut défendre le loyer ou aller le chercher. Simulez une renégociation en changeant la périodicité de sortie ou la sortie forcée d'une ligne : le WALB de Synthèse!C39 se met à jour immédiatement.</t>
+    <t>Pour voir dans l'ordre les baux à renégocier, triez la grille sur la colonne Q. Le tri demande d'ôter d'abord la protection de la feuille, par l'onglet Révision, sans mot de passe : Excel refuse de trier une plage qui contient des colonnes calculées, et ce sont justement elles qui doivent suivre leur ligne. Sélectionnez toujours la plage entière, Rent roll!B11:X50, colonnes calculées comprises : si vous ne triez que les colonnes violettes, les colonnes blanches restent en place et chaque ligne se retrouve avec les calculs d'une autre. Remettez la protection ensuite. Pour filtrer, rien à ôter : le filtre automatique est en place sur la ligne d'en-tête et la protection l'autorise. Pour chaque bail, la colonne L dit s'il faut défendre le loyer ou aller le chercher. Simulez une renégociation en changeant la périodicité de sortie ou la sortie forcée d'une ligne : le WALB de Synthèse!C39 se met à jour immédiatement.</t>
   </si>
   <si>
     <t>Vous montez un financement</t>
@@ -743,10 +743,10 @@
     <t>L'état locatif lot par lot : loyer facial et loyer économique, valeur locative de marché, prochaine faculté de sortie et durées résiduelles.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
-  </si>
-  <si>
-    <t>Une ligne par lot. La grille accepte 40 baux, lignes 11 à 50 : ajoutez vos lots à la suite, dans les lignes bleues déjà prêtes, sans jamais insérer de ligne. Aucune cellule n'est fusionnée. Le filtre automatique est posé sur la ligne d'en-tête et la protection l'autorise : filtrez sans rien déverrouiller. Pour trier, ôtez d'abord la protection par l'onglet Révision, puis triez la plage entière, colonnes calculées comprises, et remettez la protection.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
+  </si>
+  <si>
+    <t>Une ligne par lot. La grille accepte 40 baux, lignes 11 à 50 : ajoutez vos lots à la suite, dans les lignes violettes déjà prêtes, sans jamais insérer de ligne. Aucune cellule n'est fusionnée. Le filtre automatique est posé sur la ligne d'en-tête et la protection l'autorise : filtrez sans rien déverrouiller. Pour trier, ôtez d'abord la protection par l'onglet Révision, puis triez la plage entière, colonnes calculées comprises, et remettez la protection.</t>
   </si>
   <si>
     <t>Date d'analyse</t>
@@ -1591,7 +1591,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1607,12 +1607,12 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1629,13 +1629,13 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1648,12 +1648,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1663,7 +1663,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2058,6 +2058,204 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="23326725" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23326725" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9763125" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9763125" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10467975" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10467975" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13792200" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13792200" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8782050" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8782050" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3459,13 +3657,14 @@
     <mergeCell ref="B55:E55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:X66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6235,6 +6434,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
@@ -6814,13 +7014,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF0B8578"/>
+    <tabColor rgb="FF8B7CC4"/>
   </sheetPr>
   <dimension ref="B1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7553,6 +7754,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8059,13 +8261,14 @@
     <mergeCell ref="B46:F46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8463,5 +8666,6 @@
     <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>